--- a/data/trans_dic/P12_2_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P12_2_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que refirió mucha energía alguna vez o algunas veces</t>
+          <t>Población que refirió mucha energía alguna vez o algunas veces (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,43; 21,54</t>
+          <t>15,8; 21,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,28; 19,33</t>
+          <t>13,39; 19,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,98; 21,05</t>
+          <t>14,74; 21,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,74; 23,71</t>
+          <t>17,72; 23,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,04; 32,76</t>
+          <t>26,02; 32,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,77; 28,54</t>
+          <t>21,67; 28,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,25; 25,74</t>
+          <t>19,39; 25,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,01; 25,74</t>
+          <t>20,89; 25,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21,5; 26,07</t>
+          <t>21,61; 26,15</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18,23; 22,88</t>
+          <t>18,36; 22,82</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,06; 22,45</t>
+          <t>18,02; 22,29</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,03; 24,09</t>
+          <t>20,08; 24,08</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,93; 24,44</t>
+          <t>18,88; 24,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,35; 16,96</t>
+          <t>12,41; 16,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,39; 16,85</t>
+          <t>12,51; 17,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,05; 14,18</t>
+          <t>5,07; 14,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,75; 36,27</t>
+          <t>30,17; 36,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,15; 25,58</t>
+          <t>20,24; 25,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,25; 25,7</t>
+          <t>19,78; 25,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>19,27; 23,63</t>
+          <t>19,29; 23,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25,27; 29,45</t>
+          <t>25,35; 29,49</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,23; 20,63</t>
+          <t>16,97; 20,64</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,08; 20,58</t>
+          <t>17,09; 20,47</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,41; 17,9</t>
+          <t>10,47; 17,94</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,08; 19,98</t>
+          <t>14,38; 20,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,38; 21,08</t>
+          <t>14,98; 21,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,48; 17,65</t>
+          <t>12,67; 17,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,51; 18,0</t>
+          <t>12,39; 18,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,69; 27,22</t>
+          <t>20,66; 27,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,35; 27,66</t>
+          <t>21,71; 27,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,58; 23,33</t>
+          <t>17,37; 23,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,15; 22,68</t>
+          <t>8,47; 22,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,22; 22,42</t>
+          <t>17,91; 22,27</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19,52; 23,6</t>
+          <t>19,3; 23,8</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,58; 19,53</t>
+          <t>15,71; 19,79</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,43; 19,08</t>
+          <t>10,81; 19,32</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,64; 22,71</t>
+          <t>17,79; 22,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,82; 23,5</t>
+          <t>17,98; 23,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,46; 18,14</t>
+          <t>13,46; 18,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,92; 22,21</t>
+          <t>16,91; 21,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,0; 33,61</t>
+          <t>27,96; 33,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,29; 32,29</t>
+          <t>26,25; 32,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,7; 25,96</t>
+          <t>20,8; 26,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,66; 27,25</t>
+          <t>19,85; 27,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23,8; 27,42</t>
+          <t>23,62; 27,55</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22,97; 26,94</t>
+          <t>23,12; 27,01</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,03; 21,63</t>
+          <t>17,98; 21,54</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,87; 24,33</t>
+          <t>19,74; 24,15</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,28; 21,04</t>
+          <t>18,2; 21,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,01; 18,69</t>
+          <t>15,92; 18,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,49; 17,0</t>
+          <t>14,5; 16,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,14; 17,46</t>
+          <t>12,16; 17,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,97; 31,19</t>
+          <t>28,09; 31,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,99; 26,97</t>
+          <t>24,05; 27,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,88; 23,83</t>
+          <t>20,88; 23,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>17,3; 23,51</t>
+          <t>17,9; 23,45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>23,52; 25,71</t>
+          <t>23,6; 25,71</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20,45; 22,52</t>
+          <t>20,49; 22,5</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18,06; 20,08</t>
+          <t>18,1; 19,97</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,43; 20,26</t>
+          <t>16,5; 20,24</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que refirió mucha energía alguna vez o algunas veces</t>
+          <t>Población que refirió mucha energía alguna vez o algunas veces (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>107063; 149512</t>
+          <t>109687; 148345</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>93321; 135788</t>
+          <t>94031; 133876</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>100922; 141771</t>
+          <t>99304; 142393</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>112710; 150651</t>
+          <t>112615; 150576</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>179232; 225489</t>
+          <t>179097; 225727</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>151532; 198688</t>
+          <t>150858; 198263</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>129203; 172719</t>
+          <t>130154; 173378</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>141993; 173964</t>
+          <t>141178; 174291</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>297219; 360436</t>
+          <t>298741; 361517</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>254941; 319991</t>
+          <t>256723; 319120</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>242871; 301910</t>
+          <t>242341; 299750</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>262676; 315829</t>
+          <t>263232; 315683</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>182046; 235102</t>
+          <t>181599; 234688</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>125583; 172494</t>
+          <t>126180; 172119</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>126527; 172079</t>
+          <t>127752; 174691</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>72112; 169058</t>
+          <t>60455; 171488</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>288105; 351196</t>
+          <t>292211; 352719</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>207730; 263796</t>
+          <t>208658; 264341</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>211239; 268007</t>
+          <t>206266; 265395</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>184316; 226037</t>
+          <t>184554; 227769</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>487852; 568460</t>
+          <t>489247; 569150</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>352877; 422490</t>
+          <t>347523; 422666</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>352515; 424785</t>
+          <t>352900; 422565</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>223572; 384557</t>
+          <t>225020; 385430</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>95517; 135536</t>
+          <t>97568; 138396</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>116559; 159707</t>
+          <t>113525; 161151</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>94652; 133894</t>
+          <t>96131; 135244</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>88133; 126864</t>
+          <t>87286; 129078</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>141486; 186113</t>
+          <t>141252; 184987</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>164870; 213586</t>
+          <t>167667; 213735</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>137365; 182334</t>
+          <t>135799; 182576</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>85361; 211704</t>
+          <t>79029; 212000</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>248276; 305487</t>
+          <t>244003; 303448</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>298600; 361067</t>
+          <t>295190; 364127</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>239887; 300727</t>
+          <t>241902; 304839</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>170910; 312487</t>
+          <t>177150; 316477</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>166179; 213973</t>
+          <t>167606; 216409</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>168746; 222540</t>
+          <t>170202; 221310</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>126015; 169882</t>
+          <t>126018; 170097</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>156782; 205861</t>
+          <t>156728; 203713</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>290765; 349027</t>
+          <t>290352; 348973</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>276574; 339652</t>
+          <t>276083; 337036</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>215814; 270709</t>
+          <t>216879; 273017</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>214831; 297819</t>
+          <t>216951; 298494</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>471347; 543156</t>
+          <t>467829; 545728</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>459072; 538505</t>
+          <t>462090; 539779</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>356864; 428057</t>
+          <t>355899; 426374</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>401259; 491299</t>
+          <t>398731; 487682</t>
         </is>
       </c>
     </row>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1331981</t>
+          <t>1331980</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>598980; 689419</t>
+          <t>596418; 688815</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>548288; 639920</t>
+          <t>545171; 638447</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>491393; 576178</t>
+          <t>491489; 575962</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>419986; 604028</t>
+          <t>420698; 606902</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>945138; 1053966</t>
+          <t>949121; 1056738</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>852035; 957667</t>
+          <t>854156; 962705</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>738735; 843103</t>
+          <t>738815; 839917</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>632844; 859981</t>
+          <t>654772; 858035</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1565663; 1710947</t>
+          <t>1570526; 1711115</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1426614; 1570610</t>
+          <t>1429118; 1569444</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1251189; 1390966</t>
+          <t>1254017; 1383754</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1169148; 1441937</t>
+          <t>1174208; 1440269</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P12_2_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P12_2_R-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,76%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,8; 21,37</t>
+          <t>15,42; 21,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,39; 19,06</t>
+          <t>13,65; 19,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,74; 21,14</t>
+          <t>14,97; 20,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,72; 23,7</t>
+          <t>17,29; 23,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,02; 32,79</t>
+          <t>26,22; 32,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,67; 28,48</t>
+          <t>21,8; 28,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,39; 25,83</t>
+          <t>19,21; 25,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>20,89; 25,79</t>
+          <t>20,81; 25,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21,61; 26,15</t>
+          <t>21,91; 26,54</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18,36; 22,82</t>
+          <t>18,3; 22,63</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,02; 22,29</t>
+          <t>17,95; 22,46</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,08; 24,08</t>
+          <t>19,84; 23,85</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>17,41%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,88; 24,4</t>
+          <t>18,91; 24,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,41; 16,93</t>
+          <t>12,46; 16,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,51; 17,1</t>
+          <t>12,57; 16,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,07; 14,39</t>
+          <t>11,35; 15,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,17; 36,42</t>
+          <t>29,96; 36,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,24; 25,64</t>
+          <t>20,09; 26,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,78; 25,45</t>
+          <t>20,15; 25,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>19,29; 23,81</t>
+          <t>18,97; 23,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25,35; 29,49</t>
+          <t>25,02; 29,19</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16,97; 20,64</t>
+          <t>16,74; 20,49</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,09; 20,47</t>
+          <t>16,9; 20,3</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,47; 17,94</t>
+          <t>15,93; 19,17</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>19,85%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,38; 20,4</t>
+          <t>14,12; 20,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,98; 21,27</t>
+          <t>15,61; 21,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,67; 17,83</t>
+          <t>12,56; 18,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,39; 18,32</t>
+          <t>13,1; 18,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,66; 27,05</t>
+          <t>20,34; 26,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,71; 27,68</t>
+          <t>21,62; 28,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,37; 23,36</t>
+          <t>17,1; 23,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,47; 22,71</t>
+          <t>21,6; 26,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,91; 22,27</t>
+          <t>18,19; 22,58</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19,3; 23,8</t>
+          <t>19,39; 23,97</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,71; 19,79</t>
+          <t>15,83; 19,74</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,81; 19,32</t>
+          <t>17,98; 21,87</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,5%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,79; 22,97</t>
+          <t>17,55; 22,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,98; 23,37</t>
+          <t>17,91; 23,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,46; 18,16</t>
+          <t>13,62; 18,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,91; 21,98</t>
+          <t>16,65; 21,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,96; 33,6</t>
+          <t>27,73; 33,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,25; 32,04</t>
+          <t>26,28; 32,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,8; 26,18</t>
+          <t>20,91; 26,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,85; 27,31</t>
+          <t>23,31; 27,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23,62; 27,55</t>
+          <t>23,53; 27,82</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23,12; 27,01</t>
+          <t>22,89; 26,95</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,98; 21,54</t>
+          <t>17,82; 21,59</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,74; 24,15</t>
+          <t>20,87; 24,24</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>20,28%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,2; 21,02</t>
+          <t>18,06; 20,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,92; 18,65</t>
+          <t>15,99; 18,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,5; 16,99</t>
+          <t>14,51; 16,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,16; 17,55</t>
+          <t>15,64; 18,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>28,09; 31,27</t>
+          <t>28,22; 31,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,05; 27,11</t>
+          <t>24,02; 27,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,88; 23,74</t>
+          <t>20,79; 23,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>17,9; 23,45</t>
+          <t>22,21; 24,61</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>23,6; 25,71</t>
+          <t>23,63; 25,77</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20,49; 22,5</t>
+          <t>20,47; 22,53</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18,1; 19,97</t>
+          <t>18,04; 20,07</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,5; 20,24</t>
+          <t>19,35; 21,16</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>129849</t>
+          <t>140187</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>157135</t>
+          <t>169586</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>286985</t>
+          <t>309773</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>109687; 148345</t>
+          <t>107024; 147430</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>94031; 133876</t>
+          <t>95912; 135969</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>99304; 142393</t>
+          <t>100819; 140472</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>112615; 150576</t>
+          <t>119429; 162561</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>179097; 225727</t>
+          <t>180472; 226945</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>150858; 198263</t>
+          <t>151722; 196942</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>130154; 173378</t>
+          <t>128920; 173508</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>141178; 174291</t>
+          <t>152563; 188040</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>298741; 361517</t>
+          <t>302904; 366929</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>256723; 319120</t>
+          <t>256013; 316472</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>242341; 299750</t>
+          <t>241355; 302078</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>263232; 315683</t>
+          <t>282549; 339512</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>127674</t>
+          <t>142414</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>204400</t>
+          <t>226192</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>332074</t>
+          <t>368606</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>181599; 234688</t>
+          <t>181900; 233768</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>126180; 172119</t>
+          <t>126733; 172755</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>127752; 174691</t>
+          <t>128384; 172579</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>60455; 171488</t>
+          <t>118915; 165092</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>292211; 352719</t>
+          <t>290162; 352549</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>208658; 264341</t>
+          <t>207139; 268694</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>206266; 265395</t>
+          <t>210132; 265495</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>184554; 227769</t>
+          <t>202841; 249464</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>489247; 569150</t>
+          <t>482999; 563515</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>347523; 422666</t>
+          <t>342921; 419721</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>352900; 422565</t>
+          <t>348963; 418980</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>225020; 385430</t>
+          <t>337372; 405920</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>108019</t>
+          <t>125172</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>157196</t>
+          <t>195452</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>265215</t>
+          <t>320624</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>97568; 138396</t>
+          <t>95800; 136469</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>113525; 161151</t>
+          <t>118272; 162247</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>96131; 135244</t>
+          <t>95272; 136879</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>87286; 129078</t>
+          <t>105165; 149728</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>141252; 184987</t>
+          <t>139089; 184188</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>167667; 213735</t>
+          <t>166988; 217287</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>135799; 182576</t>
+          <t>133636; 180989</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>79029; 212000</t>
+          <t>175475; 219240</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>244003; 303448</t>
+          <t>247798; 307622</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>295190; 364127</t>
+          <t>296668; 366670</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>241902; 304839</t>
+          <t>243829; 304103</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>177150; 316477</t>
+          <t>290465; 353202</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>179448</t>
+          <t>188437</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>268259</t>
+          <t>285664</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>447707</t>
+          <t>474102</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>167606; 216409</t>
+          <t>165390; 211830</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>170202; 221310</t>
+          <t>169541; 224372</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>126018; 170097</t>
+          <t>127573; 170521</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>156728; 203713</t>
+          <t>164838; 216136</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>290352; 348973</t>
+          <t>288056; 348977</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>276083; 337036</t>
+          <t>276403; 338154</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>216879; 273017</t>
+          <t>218000; 274149</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>216951; 298494</t>
+          <t>260339; 308692</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>467829; 545728</t>
+          <t>466090; 550987</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>462090; 539779</t>
+          <t>457551; 538565</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>355899; 426374</t>
+          <t>352607; 427294</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>398731; 487682</t>
+          <t>439766; 510679</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>544990</t>
+          <t>596210</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>786991</t>
+          <t>876895</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1331980</t>
+          <t>1473105</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>596418; 688815</t>
+          <t>591793; 681939</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>545171; 638447</t>
+          <t>547437; 641713</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>491489; 575962</t>
+          <t>491833; 575631</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>420698; 606902</t>
+          <t>552243; 642562</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>949121; 1056738</t>
+          <t>953571; 1057287</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>854156; 962705</t>
+          <t>852908; 959982</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>738815; 839917</t>
+          <t>735629; 842539</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>654772; 858035</t>
+          <t>828645; 918372</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1570526; 1711115</t>
+          <t>1573002; 1715364</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1429118; 1569444</t>
+          <t>1427648; 1571345</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1254017; 1383754</t>
+          <t>1249836; 1390239</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1174208; 1440269</t>
+          <t>1405651; 1536612</t>
         </is>
       </c>
     </row>
